--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo_Inversores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo_Baterias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catalogo_Inversores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catalogo_Baterias" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="29.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5669,6 +5669,147 @@
       </c>
       <c r="N105" t="n">
         <v>6000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Growatt MAX 100KTL3 LV</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Ficha técnica oficial — sistema 1500V granja FV</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F106" t="n">
+        <v>200</v>
+      </c>
+      <c r="G106" t="n">
+        <v>200</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I106" t="n">
+        <v>850</v>
+      </c>
+      <c r="J106" t="n">
+        <v>10</v>
+      </c>
+      <c r="K106" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" t="n">
+        <v>26</v>
+      </c>
+      <c r="M106" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="N106" t="n">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Huawei SUN2000-100KTL-M1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Ficha técnica oficial — sistema 1500V granja FV</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F107" t="n">
+        <v>200</v>
+      </c>
+      <c r="G107" t="n">
+        <v>200</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I107" t="n">
+        <v>780</v>
+      </c>
+      <c r="J107" t="n">
+        <v>12</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="n">
+        <v>26</v>
+      </c>
+      <c r="M107" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="N107" t="n">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sungrow SG110CX</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ficha técnica oficial — sistema 1500V granja FV</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F108" t="n">
+        <v>200</v>
+      </c>
+      <c r="G108" t="n">
+        <v>200</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I108" t="n">
+        <v>850</v>
+      </c>
+      <c r="J108" t="n">
+        <v>12</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" t="n">
+        <v>26</v>
+      </c>
+      <c r="M108" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="N108" t="n">
+        <v>148500</v>
       </c>
     </row>
   </sheetData>
@@ -5721,6 +5862,26 @@
           <t>CATÁLOGO DE BATERÍAS — BIPV COLOMBIA  |  26 modelos  |  Alta tensión 300–870 V</t>
         </is>
       </c>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="6" t="n"/>
+      <c r="K1" s="6" t="n"/>
+      <c r="L1" s="6" t="n"/>
+      <c r="M1" s="6" t="n"/>
+      <c r="N1" s="6" t="n"/>
+      <c r="O1" s="6" t="n"/>
+      <c r="P1" s="6" t="n"/>
+      <c r="Q1" s="6" t="n"/>
+      <c r="R1" s="6" t="n"/>
+      <c r="S1" s="6" t="n"/>
+      <c r="T1" s="6" t="n"/>
+      <c r="U1" s="7" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -7613,6 +7774,25 @@
           <t>⚠ Pendiente para TODOS los modelos: DoD (%), Eficiencia RTE (%), Garantía (años), Temperatura operación, Costo (USD). Solicitar al proveedor para marcar 'Datos completos = Si'.</t>
         </is>
       </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="6" t="n"/>
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
+      <c r="T31" s="6" t="n"/>
+      <c r="U31" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catalogo_Inversores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Catalogo_Baterias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo_Inversores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo_Baterias" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N108"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="29.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5810,6 +5810,38 @@
       </c>
       <c r="N108" t="n">
         <v>148500</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Woodward IDS SOLO 500</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IDS_SOLO_500.OND (PVsyst V8.1.5, Manufacturer 2010)</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G109" t="n">
+        <v>500</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I109" t="n">
+        <v>500</v>
+      </c>
+      <c r="N109" t="n">
+        <v>600000</v>
       </c>
     </row>
   </sheetData>

--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="29.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -740,6 +740,11 @@
           <t>Potencia FV Max Recomendada (W)</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Potencia AC nominal (kW)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5842,6 +5847,51 @@
       </c>
       <c r="N109" t="n">
         <v>600000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Growatt MID15KTL3-X</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F110" t="n">
+        <v>140</v>
+      </c>
+      <c r="G110" t="n">
+        <v>140</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I110" t="n">
+        <v>293</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M110" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N110" t="n">
+        <v>22500</v>
+      </c>
+      <c r="O110" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -5882,10 +5882,10 @@
         <v>8</v>
       </c>
       <c r="L110" t="n">
-        <v>6.4</v>
+        <v>27.5</v>
       </c>
       <c r="M110" t="n">
-        <v>6.4</v>
+        <v>33.5</v>
       </c>
       <c r="N110" t="n">
         <v>22500</v>

--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:W110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="29.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,46 @@
           <t>Potencia AC nominal (kW)</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Inversor Híbrido (Si/No)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Voltaje Batería Min (V)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Voltaje Batería Max (V)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Corriente Máxima Carga Batería (A)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Confianza</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2347,6 +2387,21 @@
       <c r="N37" t="n">
         <v>1250</v>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2398,6 +2453,21 @@
       <c r="N38" t="n">
         <v>1250</v>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2449,6 +2519,21 @@
       <c r="N39" t="n">
         <v>2500</v>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2500,6 +2585,21 @@
       <c r="N40" t="n">
         <v>1250</v>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2551,6 +2651,21 @@
       <c r="N41" t="n">
         <v>2500</v>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2602,6 +2717,21 @@
       <c r="N42" t="n">
         <v>2500</v>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2653,6 +2783,21 @@
       <c r="N43" t="n">
         <v>5000</v>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2704,6 +2849,21 @@
       <c r="N44" t="n">
         <v>2500</v>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2755,6 +2915,21 @@
       <c r="N45" t="n">
         <v>5000</v>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2806,6 +2981,21 @@
       <c r="N46" t="n">
         <v>5000</v>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2857,6 +3047,21 @@
       <c r="N47" t="n">
         <v>5000</v>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2908,6 +3113,24 @@
       <c r="N48" t="n">
         <v>5000</v>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2959,6 +3182,24 @@
       <c r="N49" t="n">
         <v>5000</v>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3010,6 +3251,24 @@
       <c r="N50" t="n">
         <v>5000</v>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3061,6 +3320,24 @@
       <c r="N51" t="n">
         <v>5000</v>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3112,6 +3389,24 @@
       <c r="N52" t="n">
         <v>5000</v>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3162,6 +3457,24 @@
       </c>
       <c r="N53" t="n">
         <v>5000</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Híbrido / Off-grid</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="54">

--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W110"/>
+  <dimension ref="A1:W111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="29.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6205,6 +6205,60 @@
       </c>
       <c r="O110" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MG750TL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>INVT-MG-0.75-6kW_datasheet_2020.07_V1.0.pdf + verificado contra pantalla real PVsyst 8.1.5</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>400</v>
+      </c>
+      <c r="F111" t="n">
+        <v>60</v>
+      </c>
+      <c r="G111" t="n">
+        <v>60</v>
+      </c>
+      <c r="H111" t="n">
+        <v>350</v>
+      </c>
+      <c r="I111" t="n">
+        <v>60</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>900</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>INVT Solar Technology</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Eficiencia máxima 96,80% (idéntica en ficha oficial y pantalla PVsyst). Eficiencia Euro: 95,95% (ficha oficial) / 96,00% (PVsyst) -- diferencia menor, no resuelta. Corriente AC nominal ficha PVsyst: 3,26A (=750W/230V); corriente AC máxima ficha oficial: 3,6A (=~828W/230V, coherente con 'Potencia CA máxima 0,80kW' vista en PVsyst). Ventana MPPT de la ficha oficial 2020 es más amplia (50-400V) que la usada en la corrida real de PVsyst (60-350V) -- se usó esta última por ser la validada.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/bipv_python/datos/inversores_catalogo.xlsx
+++ b/bipv_python/datos/inversores_catalogo.xlsx
@@ -6244,6 +6244,12 @@
       <c r="K111" t="n">
         <v>1</v>
       </c>
+      <c r="L111" t="n">
+        <v>15</v>
+      </c>
+      <c r="M111" t="n">
+        <v>15</v>
+      </c>
       <c r="N111" t="n">
         <v>900</v>
       </c>
@@ -6257,7 +6263,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Eficiencia máxima 96,80% (idéntica en ficha oficial y pantalla PVsyst). Eficiencia Euro: 95,95% (ficha oficial) / 96,00% (PVsyst) -- diferencia menor, no resuelta. Corriente AC nominal ficha PVsyst: 3,26A (=750W/230V); corriente AC máxima ficha oficial: 3,6A (=~828W/230V, coherente con 'Potencia CA máxima 0,80kW' vista en PVsyst). Ventana MPPT de la ficha oficial 2020 es más amplia (50-400V) que la usada en la corrida real de PVsyst (60-350V) -- se usó esta última por ser la validada.</t>
+          <t>Eficiencia máxima 96,80% (idéntica en ficha oficial y pantalla PVsyst). Eficiencia Euro: 95,95% (ficha oficial) / 96,00% (PVsyst) -- diferencia menor, no resuelta. Corriente AC nominal ficha PVsyst: 3,26A (=750W/230V); corriente AC máxima ficha oficial: 3,6A (=~828W/230V, coherente con 'Potencia CA máxima 0,80kW' vista en PVsyst). Ventana MPPT de la ficha oficial 2020 es más amplia (50-400V) que la usada en la corrida real de PVsyst (60-350V) -- se usó esta última por ser la validada. Corriente máxima de entrada (15A): DERIVADA de 900W/60V (potencia DC máxima real / Vmppt mínimo real), no publicada directamente por ninguna fuente -- sin este valor, evaluar_compatibilidad_string() no podía evaluar ninguna configuración con este inversor.</t>
         </is>
       </c>
     </row>
